--- a/input/Classroom Data.xlsx
+++ b/input/Classroom Data.xlsx
@@ -1,67 +1,158 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hussamuddin\Seating arrangement\Exam_Seating_Arrangement\input\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34F8534D-6CE3-4CA4-815D-521E8EAFD286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Classroom Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Classroom Data" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Classroom Data'!$A$4:$B$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Classroom Data'!$A$4:$B$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Classroom Data'!$A$1:$B$27</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Classroom Data'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Classroom Data'!$A$1:$B$28</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+  <si>
+    <t>Classroom Data — Static</t>
+  </si>
+  <si>
+    <t>One student per bench/seat. Existing room capacities are retained.</t>
+  </si>
+  <si>
+    <t>Room No.</t>
+  </si>
+  <si>
+    <t>Capacity (No. of Benches/Seats)</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>204</t>
+  </si>
+  <si>
+    <t>205</t>
+  </si>
+  <si>
+    <t>206</t>
+  </si>
+  <si>
+    <t>207</t>
+  </si>
+  <si>
+    <t>208</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>213</t>
+  </si>
+  <si>
+    <t>3 A</t>
+  </si>
+  <si>
+    <t>3 B</t>
+  </si>
+  <si>
+    <t>301</t>
+  </si>
+  <si>
+    <t>302</t>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>307</t>
+  </si>
+  <si>
+    <t>308</t>
+  </si>
+  <si>
+    <t>309</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>313</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF203040"/>
       <name val="Calibri"/>
-      <color rgb="00203040"/>
-      <sz val="12"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="12"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF176245"/>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00176245"/>
-      <sz val="18"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00176245"/>
+        <fgColor rgb="FF176245"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F6FA"/>
+        <fgColor rgb="FFF2F6FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -75,118 +166,64 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BCC9D4"/>
+        <color rgb="FFBCC9D4"/>
       </left>
       <right style="thin">
-        <color rgb="00BCC9D4"/>
+        <color rgb="FFBCC9D4"/>
       </right>
       <top style="thin">
-        <color rgb="00BCC9D4"/>
+        <color rgb="FFBCC9D4"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BCC9D4"/>
+        <color rgb="FFBCC9D4"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -474,295 +511,233 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Classroom Data — Static</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>One student per bench/seat. Existing room capacities are retained.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="n"/>
-    </row>
-    <row r="4" ht="56" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Room No.</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Capacity (No. of Benches/Seats)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="6" ht="44" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
+    <row r="1" spans="1:2" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8"/>
+    </row>
+    <row r="2" spans="1:2" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8"/>
+    </row>
+    <row r="3" spans="1:2" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+    </row>
+    <row r="4" spans="1:2" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4">
         <v>16</v>
       </c>
     </row>
-    <row r="7" ht="44" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
+    <row r="6" spans="1:2" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3">
         <v>53</v>
       </c>
     </row>
-    <row r="8" ht="44" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
+    <row r="7" spans="1:2" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4">
         <v>65</v>
       </c>
     </row>
-    <row r="9" ht="44" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
+    <row r="8" spans="1:2" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3">
         <v>64</v>
       </c>
     </row>
-    <row r="10" ht="44" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
+    <row r="9" spans="1:2" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4">
         <v>22</v>
       </c>
     </row>
-    <row r="11" ht="44" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
+    <row r="10" spans="1:2" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3">
         <v>64</v>
       </c>
     </row>
-    <row r="12" ht="44" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
+    <row r="11" spans="1:2" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4">
         <v>61</v>
       </c>
     </row>
-    <row r="13" ht="44" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
+    <row r="12" spans="1:2" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3">
         <v>53</v>
       </c>
     </row>
-    <row r="14" ht="44" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
+    <row r="13" spans="1:2" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4">
         <v>34</v>
       </c>
     </row>
-    <row r="15" ht="44" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
+    <row r="14" spans="1:2" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3">
         <v>25</v>
       </c>
     </row>
-    <row r="16" ht="44" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n">
+    <row r="15" spans="1:2" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4">
         <v>26</v>
       </c>
     </row>
-    <row r="17" ht="44" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>3 A</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
+    <row r="16" spans="1:2" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3">
         <v>38</v>
       </c>
     </row>
-    <row r="18" ht="44" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>3 B</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n">
+    <row r="17" spans="1:2" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4">
         <v>37</v>
       </c>
     </row>
-    <row r="19" ht="44" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
+    <row r="18" spans="1:2" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3">
         <v>12</v>
       </c>
     </row>
-    <row r="20" ht="44" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n">
+    <row r="19" spans="1:2" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4">
         <v>56</v>
       </c>
     </row>
-    <row r="21" ht="44" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
+    <row r="20" spans="1:2" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3">
         <v>56</v>
       </c>
     </row>
-    <row r="22" ht="44" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
+    <row r="21" spans="1:2" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4">
         <v>57</v>
       </c>
     </row>
-    <row r="23" ht="44" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n">
+    <row r="22" spans="1:2" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3">
         <v>66</v>
       </c>
     </row>
-    <row r="24" ht="44" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
+    <row r="23" spans="1:2" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4">
         <v>32</v>
       </c>
     </row>
-    <row r="25" ht="44" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="n">
+    <row r="24" spans="1:2" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3">
         <v>22</v>
       </c>
     </row>
-    <row r="26" ht="44" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n">
+    <row r="25" spans="1:2" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4">
         <v>23</v>
       </c>
     </row>
-    <row r="27" ht="44" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n">
+    <row r="26" spans="1:2" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3">
         <v>60</v>
       </c>
     </row>
-    <row r="28" ht="44" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n">
+    <row r="27" spans="1:2" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4">
         <v>66</v>
       </c>
     </row>
+    <row r="28" spans="1:2" ht="44.1" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A4:B28"/>
+  <autoFilter ref="A4:B27" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
 </worksheet>
 </file>